--- a/artfynd/A 38264-2026 artfynd.xlsx
+++ b/artfynd/A 38264-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438274</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137438277</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137438275</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38264-2026 artfynd.xlsx
+++ b/artfynd/A 38264-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438274</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137438277</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137438275</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38264-2026 artfynd.xlsx
+++ b/artfynd/A 38264-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137438274</v>
+        <v>137552239</v>
       </c>
       <c r="B2" t="n">
-        <v>93523</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lydinge, Upl</t>
+          <t>Österunda kyrka, 2,1 km N-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618732</v>
+        <v>618805</v>
       </c>
       <c r="R2" t="n">
-        <v>6635033</v>
+        <v>6634805</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,57 +756,57 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles tallskog med en hel del gulvit renlav, grå renlav och islandslav</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438274</t>
+          <t>https://artportalen.se/Sighting/137552239</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137438277</v>
+        <v>137438274</v>
       </c>
       <c r="B3" t="n">
-        <v>80154</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +814,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618852</v>
+        <v>618732</v>
       </c>
       <c r="R3" t="n">
-        <v>6634884</v>
+        <v>6635033</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,55 +909,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438277</t>
+          <t>https://artportalen.se/Sighting/137438274</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137438276</v>
+        <v>137552238</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lydinge, Upl</t>
+          <t>Nysätra kyrka, 2,3 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618894</v>
+        <v>618847</v>
       </c>
       <c r="R4" t="n">
-        <v>6635033</v>
+        <v>6634874</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,22 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,66 +1000,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438276</t>
+          <t>https://artportalen.se/Sighting/137552238</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137438278</v>
+        <v>137552241</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lydinge, Upl</t>
+          <t>Österunda kyrka, 2,2 km N-ut, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618853</v>
+        <v>618734</v>
       </c>
       <c r="R5" t="n">
-        <v>6634868</v>
+        <v>6634782</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,22 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,71 +1106,66 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438278</t>
+          <t>https://artportalen.se/Sighting/137552241</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137438275</v>
+        <v>137438277</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>80158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lydinge, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618883</v>
+        <v>618852</v>
       </c>
       <c r="R6" t="n">
-        <v>6635006</v>
+        <v>6634884</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1232,353 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137438277</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137438276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>618894</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6635033</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137438276</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137438278</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618853</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6634868</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137438278</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137438275</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618883</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6635006</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137438275</t>
         </is>
@@ -1256,6 +1591,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
